--- a/vse-loti/340033533/spec-340033533.xlsx
+++ b/vse-loti/340033533/spec-340033533.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -450,35 +450,40 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Наименование позиции (⌀ + s, если указано)</t>
+          <t>Наименование позиции</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>D×s, мм</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Кол-во (исх.)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Ед. изм.</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Масса, т (приведённая)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Стоимость (без НДС)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Цена за т (без НДС)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Цена за т (с НДС)</t>
         </is>

--- a/vse-loti/340033533/spec-340033533.xlsx
+++ b/vse-loti/340033533/spec-340033533.xlsx
@@ -16,8 +16,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="3">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="#,##0.####"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00&quot; ₽&quot;"/>
+  </numFmts>
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,11 +29,19 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <b val="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="3">
@@ -46,7 +57,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -54,16 +65,36 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,20 +460,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="15.28515625" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="20.28515625" customWidth="1" min="7" max="7"/>
+    <col width="18.85546875" customWidth="1" min="8" max="8"/>
+    <col width="16.42578125" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>№</t>
@@ -490,20 +522,57 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>м. м</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" s="3" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Источник: Razdel IV - Tekhnicheskoe zadanie_opory.txt</t>
-        </is>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>НМЦК из обоснования:</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>2074393</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Источник: spec-340033533.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
+    <row r="8"/>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A6:B8"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/vse-loti/340033533/spec-340033533.xlsx
+++ b/vse-loti/340033533/spec-340033533.xlsx
@@ -16,9 +16,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="#,##0.####"/>
-    <numFmt numFmtId="165" formatCode="#,##0.00&quot; ₽&quot;"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0.00&quot; ₽&quot;"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -36,11 +35,11 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <b val="1"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <b val="1"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -83,16 +82,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -460,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -522,56 +519,34 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>м. м</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" s="3" t="n">
-        <v>5.11</v>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>ИТОГО</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>ИТОГО</t>
-        </is>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>НМЦК из обоснования:</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>2074393.6</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>НМЦК из обоснования:</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="n">
-        <v>2074393</v>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Источник: Извещение ОЗК СМСП.docx</t>
+        </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Источник: spec-340033533.txt</t>
-        </is>
-      </c>
-    </row>
+    <row r="6"/>
     <row r="7"/>
-    <row r="8"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:B8"/>
+    <mergeCell ref="A5:B7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
